--- a/Sheikhpura_Health_PIP_Website_Database.xlsx
+++ b/Sheikhpura_Health_PIP_Website_Database.xlsx
@@ -26,17 +26,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facilities" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Doctors" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Departments" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grievance_Categories" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grievances" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Settings'!$A$1:$E$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Navigation'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Navigation'!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Financial_Years'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Program_Categories'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Programs_FMR'!$A$1:$J$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Documents'!$A$1:$N$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Home_Content'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Home_Content'!$A$1:$K$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Important_Links'!$A$1:$K$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Notices'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contact_Information'!$A$1:$O$6</definedName>
@@ -48,7 +50,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Facilities'!$A$1:$V$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Facility_Doctors'!$A$1:$H$403</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Facility_Departments'!$A$1:$G$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'_Lists'!$A$1:$C$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Grievance_Categories'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Grievances'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'_Lists'!$A$1:$C$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -586,7 +590,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Notices (weekly), Documents and PIP_Documents (whenever a file is published), Programs_FMR (once a year), Financial_Years (once a year).</t>
+          <t>Notices (weekly), Documents (whenever a file is published), Programs_FMR (once a year), Financial_Years (once a year). Review Grievances weekly from the Admin dashboard — never edit that sheet directly.</t>
         </is>
       </c>
     </row>
@@ -692,8 +696,25 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Grievances is different from every other sheet</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>It holds resident names, phone numbers and complaint text submitted through grievance.html. It is never sent to the public website — not even in stripped form, unlike Facility_Doctors. Review and update it only from the Admin dashboard's Grievances panel, never by editing this sheet directly.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42650,11 +42671,358 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Category_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Display_Order</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GCAT01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Facility Cleanliness / Hygiene</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GCAT02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Staff Behaviour</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GCAT03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Medicine Availability</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GCAT04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Doctor / Staff Availability</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GCAT05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Waiting Time</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GCAT06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ambulance Service</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GCAT07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Corruption / Bribery Demand</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GCAT08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure / Equipment</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GCAT09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Suggestion for Improvement</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GCAT10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D11"/>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_Lists!$B$2:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grievance_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Citizen_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Citizen_Phone</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Resolution_Note</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Internal_Notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Submitted_Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Updated_Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Resolved_Date</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="F2:F501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_Lists!$B$66:$B$69</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_Lists!$B$19:$B$21</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0098A2B3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43659,8 +44027,76 @@
       </c>
       <c r="C65" s="2" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Grievance_Status</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Just submitted, not yet reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Grievance_Status</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>DCCC is looking into it</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Grievance_Status</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Addressed — a Resolution_Note is shown to the citizen</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Grievance_Status</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>No further action — duplicate, spam or out of scope</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C65"/>
+  <autoFilter ref="A1:C69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43671,7 +44107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43833,22 +44269,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NAV03</t>
+          <t>NAV10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Free Services</t>
+          <t>File a Complaint</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>नि:शुल्क सेवाएं</t>
+          <t>शिकायत दर्ज करें</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>benefits.html</t>
+          <t>grievance.html</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -43867,7 +44303,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -43879,22 +44315,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NAV04</t>
+          <t>NAV03</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Health Programmes</t>
+          <t>Free Services</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>स्वास्थ्य कार्यक्रम</t>
+          <t>नि:शुल्क सेवाएं</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>programmes.html</t>
+          <t>benefits.html</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -43913,7 +44349,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -43925,22 +44361,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NAV05</t>
+          <t>NAV04</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Events &amp; News</t>
+          <t>Health Programmes</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>कार्यक्रम एवं समाचार</t>
+          <t>स्वास्थ्य कार्यक्रम</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>events.html</t>
+          <t>programmes.html</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -43959,7 +44395,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>bell</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -43971,22 +44407,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NAV06</t>
+          <t>NAV05</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Notices</t>
+          <t>Events &amp; News</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>सूचनाएँ</t>
+          <t>कार्यक्रम एवं समाचार</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>notices.html</t>
+          <t>events.html</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -44017,22 +44453,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NAV07</t>
+          <t>NAV06</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Notices</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>दस्तावेज़</t>
+          <t>सूचनाएँ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>documents.html</t>
+          <t>notices.html</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -44051,7 +44487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>bell</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -44063,22 +44499,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NAV08</t>
+          <t>NAV07</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>संपर्क करें</t>
+          <t>दस्तावेज़</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>contact.html</t>
+          <t>documents.html</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -44097,7 +44533,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>download</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -44109,22 +44545,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NAV09</t>
+          <t>NAV08</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>BHAVYA Portal</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>भव्य पोर्टल</t>
+          <t>संपर्क करें</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://mera.bhavyabiharhealth.in/</t>
+          <t>contact.html</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -44138,24 +44574,70 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>_self</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>NAV09</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>BHAVYA Portal</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>भव्य पोर्टल</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://mera.bhavyabiharhealth.in/</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>External</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>_blank</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J11"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=_Lists!$B$26:$B$27</formula1>
     </dataValidation>
   </dataValidations>
@@ -52420,7 +52902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -53158,10 +53640,61 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>sec_grievance</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Have a Complaint or Suggestion?</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>शिकायत या सुझाव है?</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Tell us — we will follow up</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Report an issue at a government health facility, or suggest an improvement. The District Control Command Centre reviews every submission each week and calls you back.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>grievance.html</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>File a Complaint</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K17"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=_Lists!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
